--- a/docs/UAT-Data-Migrate/UAT-นำเข้าข้อมูล-งบประมาณ-2569-08-30.xlsx
+++ b/docs/UAT-Data-Migrate/UAT-นำเข้าข้อมูล-งบประมาณ-2569-08-30.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ปกและลงนาม" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="สรุปประเภทข้อมูล" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ยืนยัน-แหล่งเงิน" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ยืนยัน-กลุ่มงบ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ยืนยัน-กลุ่มงบ-วัสดุ" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ยืนยัน-วัสดุย่อย" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ยืนยัน-ประเภทงบ" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ยืนยัน-กลุ่มครุภัณฑ์" sheetId="7" state="visible" r:id="rId7"/>
@@ -23,9 +22,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="วิธีตรวจและเกณฑ์" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'สรุปประเภทข้อมูล'!$A$1:$P$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'สรุปประเภทข้อมูล'!$A$1:$R$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ยืนยัน-แหล่งเงิน'!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ยืนยัน-กลุ่มงบ'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ยืนยัน-กลุ่มงบ-วัสดุ'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ยืนยัน-วัสดุย่อย'!$A$1:$I$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'ยืนยัน-ประเภทงบ'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'ยืนยัน-กลุ่มครุภัณฑ์'!$A$1:$H$16</definedName>
@@ -36,14 +35,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'ยืนยัน-แผนปี'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'ยืนยัน-หมวดงบ'!$A$1:$D$45</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,19 +53,85 @@
     <font>
       <name val="Prompt"/>
       <b val="1"/>
-      <color rgb="000F7A72"/>
+      <color rgb="FF0F7A72"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Prompt"/>
       <b val="1"/>
-      <color rgb="00123A56"/>
+      <color rgb="FF123A56"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="Prompt"/>
-      <color rgb="005B6878"/>
+      <color rgb="FF5B6878"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Prompt"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Prompt"/>
+      <color rgb="FF2F3A48"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Prompt"/>
+      <b val="1"/>
+      <color rgb="FF2F3A48"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Prompt"/>
+      <color rgb="FF2F3A48"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Prompt"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Prompt"/>
+      <b val="1"/>
+      <color rgb="FF0F7A72"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Prompt"/>
+      <b val="1"/>
+      <color rgb="FF123A56"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Prompt"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Prompt-Regular"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Prompt-Regular"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Prompt-Regular"/>
+      <color rgb="FF2F3A48"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Prompt-Regular"/>
+      <b val="1"/>
+      <color rgb="FF0F7A72"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Prompt"/>
@@ -82,34 +147,11 @@
     <font>
       <name val="Prompt"/>
       <b val="1"/>
-      <color rgb="002F3A48"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Prompt"/>
-      <color rgb="002F3A48"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Prompt"/>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
-    <font>
-      <name val="Prompt"/>
-      <b val="1"/>
-      <color rgb="000F7A72"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Prompt"/>
-      <b val="1"/>
-      <color rgb="00123A56"/>
-      <sz val="16"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -118,12 +160,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00123A56"/>
+        <fgColor rgb="FF123A56"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5F5F3"/>
+        <fgColor rgb="FFE5F5F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F7A72"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F5EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECEA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4E4C8"/>
       </patternFill>
     </fill>
     <fill>
@@ -133,25 +195,74 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5F5EA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBECEA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4E4C8"/>
+        <fgColor rgb="00123A56"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD7DEE6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD7DEE6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD7DEE6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD7DEE6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD7DEE6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD7DEE6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD7DEE6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD7DEE6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD7DEE6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD7DEE6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD7DEE6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD7DEE6"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -173,19 +284,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -195,9 +300,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -227,22 +329,63 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
       <font>
         <name val="Prompt"/>
         <b val="1"/>
-        <color rgb="002C7A45"/>
+        <color rgb="FF8A5A00"/>
         <sz val="11"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00E5F5EA"/>
+          <fgColor rgb="FFF4E4C8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -250,12 +393,12 @@
       <font>
         <name val="Prompt"/>
         <b val="1"/>
-        <color rgb="00B4433A"/>
+        <color rgb="FFB4433A"/>
         <sz val="11"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FBECEA"/>
+          <fgColor rgb="FFFBECEA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -263,12 +406,12 @@
       <font>
         <name val="Prompt"/>
         <b val="1"/>
-        <color rgb="008A5A00"/>
+        <color rgb="FF2C7A45"/>
         <sz val="11"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00F4E4C8"/>
+          <fgColor rgb="FFE5F5EA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -635,284 +778,310 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="34" customHeight="1"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" style="18" min="1" max="1"/>
+    <col width="26" customWidth="1" style="18" min="2" max="2"/>
+    <col width="36" customWidth="1" style="18" min="3" max="3"/>
+    <col width="22" customWidth="1" style="18" min="4" max="4"/>
+    <col width="18" customWidth="1" style="18" min="5" max="6"/>
+    <col width="16" customWidth="1" style="18" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="34" customHeight="1" s="18">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>โรงพยาบาลวชิระภูเก็ต</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+    <row r="3" ht="34" customHeight="1" s="18">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>ยืนยันข้อมูลนำเข้า ระบบงบประมาณ</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="3" t="inlineStr">
+    <row r="4" ht="34" customHeight="1" s="18">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>เอกสารสรุปประเภทข้อมูลนำเข้า · จำนวน record ในระบบ · รายการให้ผู้ใช้ยืนยันและลงนาม (Sign-off)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="4" t="inlineStr">
+    <row r="6" ht="34" customHeight="1" s="18">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>ระบบ</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Odoo 18 · vpk_budget และบัญชีวิเคราะห์</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="4" t="inlineStr">
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="21" t="n"/>
+    </row>
+    <row r="7" ht="34" customHeight="1" s="18">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>รหัสเอกสาร</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>DM-SIGNOFF-BUD-001</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="4" t="inlineStr">
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="21" t="n"/>
+    </row>
+    <row r="8" ht="34" customHeight="1" s="18">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>ฐานข้อมูล</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>VPK-S1 · บริษัท โรงพยาบาลวชิระภูเก็ต</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="4" t="inlineStr">
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="21" t="n"/>
+    </row>
+    <row r="9" ht="34" customHeight="1" s="18">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>วัน-เวลาที่ดึงข้อมูล</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>30 ส.ค. 2569  23:24</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="4" t="inlineStr">
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="21" t="n"/>
+    </row>
+    <row r="10" ht="34" customHeight="1" s="18">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>เจ้าของข้อมูล</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>งานงบประมาณ</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="21" t="n"/>
+    </row>
+    <row r="11" ht="34" customHeight="1" s="18">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>ประเภท Master ที่เกี่ยวข้อง</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>11 ประเภท</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="4" t="inlineStr">
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="21" t="n"/>
+    </row>
+    <row r="12" ht="34" customHeight="1" s="18">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>Master ที่นำเข้าแล้ว</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>11 ประเภท  รวม 186 รายการ</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="4" t="inlineStr">
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="21" t="n"/>
+    </row>
+    <row r="13" ht="34" customHeight="1" s="18">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>Master ที่ยังไม่มีข้อมูล</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>ไม่มี</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="4" t="inlineStr">
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="21" t="n"/>
+    </row>
+    <row r="14" ht="34" customHeight="1" s="18">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>ข้อมูลคงค้าง</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>ไม่มีชีตคงค้างในโมดูลนี้</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="B16" s="6" t="inlineStr">
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="21" t="n"/>
+    </row>
+    <row r="16" ht="34" customHeight="1" s="18">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>วิธีใช้  1) ดูชีต “สรุปประเภทข้อมูล” ว่าแต่ละประเภทมีกี่ record  2) เปิดชีต “ยืนยัน-…” ตรวจรหัส/ชื่อที่นำเข้าแล้ว  3) ตรวจชีตคงค้าง (PO คงค้าง / เจ้าหนี้คงค้าง / TB 2569) แล้วกรอกผลยืนยัน  เกณฑ์รับรอง: จำนวนและรายการ Master ถูกต้อง · คงค้างที่ยอดเป็น 0 ให้ลงนามว่ายังไม่นำเข้า</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="18" ht="34" customHeight="1" s="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>บทบาท</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>ชื่อ-สกุล</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>ผลยืนยัน</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>ลงชื่อ</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>วันที่</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="8" t="n">
+    <row r="19" ht="34" customHeight="1" s="18">
+      <c r="A19" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>งานงบประมาณ (เจ้าของข้อมูล)</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="8" t="n">
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="19" t="n"/>
+    </row>
+    <row r="20" ht="34" customHeight="1" s="18">
+      <c r="A20" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>หน่วยงานผู้ใช้</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="8" t="n">
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="34" customHeight="1" s="18">
+      <c r="A21" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>IT / ผู้ดูแลระบบ</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="8" t="n">
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+    </row>
+    <row r="22" ht="34" customHeight="1" s="18">
+      <c r="A22" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>ผู้บริหารโครงการ</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="10" t="inlineStr">
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+    </row>
+    <row r="23" ht="34" customHeight="1" s="18">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>คำรับรอง: ข้าพเจ้าได้ตรวจประเภทข้อมูล จำนวน record และรายการที่ export แล้ว และยืนยันตามผลที่ระบุ  หากเลือก “ต้องแก้ไข/ยังไม่ครบ” ให้ระบุรายการในหมายเหตุ
 ผลภาพรวมโมดูลนี้:  รับรองให้นำไปใช้ต่อ   /   รับรองแบบมีเงื่อนไข   /   ต้องนำเข้าใหม่</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
+    <row r="24" ht="34" customHeight="1" s="18"/>
+    <row r="25" ht="34" customHeight="1" s="18"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B2:F2"/>
+    <mergeCell ref="C12:F12"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C11:F11"/>
     <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="B23:F25"/>
     <mergeCell ref="C14:F14"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B23:F25"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D19 D20 D21 D22" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D19 D20 D21 D22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"ถูกต้อง,ต้องแก้ไข,ยังไม่ครบ,ข้าม"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
   <headerFooter>
     <oddHeader>&amp;Lโรงพยาบาลวชิระภูเก็ต · ยืนยันข้อมูลนำเข้า ระบบงบประมาณ</oddHeader>
     <oddFooter>&amp;Lเอกสารยืนยันข้อมูลนำเข้า (Data Migration Sign-off) · ใช้ภายใน&amp;Rหน้า &amp;P / &amp;N</oddFooter>
@@ -931,170 +1100,169 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" style="18" min="1" max="1"/>
+    <col width="18" customWidth="1" style="18" min="2" max="2"/>
+    <col width="42" customWidth="1" style="18" min="3" max="4"/>
+    <col width="16" customWidth="1" style="18" min="5" max="5"/>
+    <col width="28" customWidth="1" style="18" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="18">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>รหัสภายใน</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>ชื่อ</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>ชื่อเต็ม</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>ผลยืนยัน</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="12" t="n">
+    <row r="2" ht="20" customHeight="1" s="18">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>โปรเจกต์</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr"/>
-      <c r="F2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="n">
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="19" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="18">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr"/>
-      <c r="F3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="19" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="18">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>งานบริการจ่ายยาผู้ป่วยใน</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>Project / งานบริการจ่ายยาผู้ป่วยใน</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="19" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="18">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>งานบริการจ่ายยาผู้ป่วยใน</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>งานบริการจ่ายยาผู้ป่วยใน</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="n">
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="19" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1" s="18">
+      <c r="A6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>งานบริบาลเภสัชกรรมผู้ป่วยในและพัฒนาระบบยา</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>งานบริบาลเภสัชกรรมผู้ป่วยในและพัฒนาระบบยา</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="n">
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="19" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1" s="18">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>งานบริการจ่ายยาผู้ป่วยนอก</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>งานบริการจ่ายยาผู้ป่วยนอก</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="19" t="n"/>
+    </row>
+    <row r="9" ht="19" customHeight="1" s="18">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>รวม 6 รายการ · แผนวิเคราะห์ / มิติหน่วยงาน · โมเดล account.analytic.plan</t>
         </is>
@@ -1103,12 +1271,12 @@
   </sheetData>
   <autoFilter ref="A1:F7"/>
   <dataValidations count="1">
-    <dataValidation sqref="E2 E3 E4 E5 E6 E7" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="E2 E3 E4 E5 E6 E7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"ถูกต้อง,ต้องแก้ไข,ยังไม่ครบ,ข้าม"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;Lโรงพยาบาลวชิระภูเก็ต · ยืนยันข้อมูลนำเข้า ระบบงบประมาณ</oddHeader>
     <oddFooter>&amp;Lเอกสารยืนยันข้อมูลนำเข้า (Data Migration Sign-off) · ใช้ภายใน&amp;Rหน้า &amp;P / &amp;N</oddFooter>
@@ -1127,1080 +1295,1080 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" style="18" min="1" max="1"/>
+    <col width="18" customWidth="1" style="18" min="2" max="2"/>
+    <col width="42" customWidth="1" style="18" min="3" max="3"/>
+    <col width="18" customWidth="1" style="18" min="4" max="4"/>
+    <col width="14" customWidth="1" style="18" min="5" max="5"/>
+    <col width="16" customWidth="1" style="18" min="6" max="6"/>
+    <col width="28" customWidth="1" style="18" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="18">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>รหัส</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>ชื่อ</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>แผน</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>สถานะ</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>ผลยืนยัน</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="12" t="n">
+    <row r="2" ht="20" customHeight="1" s="18">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>PED-001</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงาน กุมารเวชกรรม</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="n">
+      <c r="E2" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="19" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="18">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>RAD-001</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงาน รังสีวิทยา</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="19" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="18">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>UAT-DEPT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>หน่วยงานทดสอบ</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="19" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="18">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>หน่วยงานพัสดุ</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="n">
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="19" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1" s="18">
+      <c r="A6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B6" s="19" t="n"/>
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงานทันตกรรม</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="n">
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="19" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1" s="18">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="B7" s="19" t="n"/>
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงาน โภชนศาตร์</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="19" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" s="18">
+      <c r="A8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="B8" s="19" t="n"/>
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>ตรวจสุขภาพมะฮอกกานี</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="19" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="18">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="B9" s="19" t="n"/>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงานสุขศึกษา</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="n">
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="19" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1" s="18">
+      <c r="A10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>OPD SMC</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="n">
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="19" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1" s="18">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="B11" s="19" t="n"/>
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงานโครงสร้างพื้นฐานฯ</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="n">
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="19" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1" s="18">
+      <c r="A12" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงานเวชกรรมฟื้นฟู</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="n">
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="19" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1" s="18">
+      <c r="A13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>งานเคลื่อนย้ายผู้ป่วย</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="n">
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="19" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1" s="18">
+      <c r="A14" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงาน การพยาบาลชุมชน</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="19" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1" s="18">
+      <c r="A15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="B15" s="19" t="n"/>
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงานจักษุวิทยา</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="19" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" s="18">
+      <c r="A16" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="B16" s="19" t="n"/>
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>งานยานพาหนะ</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="n">
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1" s="18">
+      <c r="A17" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>งานบริหารทั่วไป</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="n">
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="19" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" s="18">
+      <c r="A18" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงานเภสัชกรรม</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="n">
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1" s="18">
+      <c r="A19" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>กลุ่มภารกิจสุขภาพดิจิทัล</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n">
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="19" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1" s="18">
+      <c r="A20" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="B20" s="19" t="n"/>
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>ศูนย์เครื่องมือแพทย์</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="n">
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1" s="18">
+      <c r="A21" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงานเทคนิคการแพทย์ฯ</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="n">
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="19" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" s="18">
+      <c r="A22" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>งานธนาคารเลือด</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="19" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" s="18">
+      <c r="A23" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงาน อาชีวเวชกรรม</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="n">
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="19" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" s="18">
+      <c r="A24" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงานอายุรกรรม</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="19" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" s="18">
+      <c r="A25" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงาน ภารกิจด้านการพยาบาล  298</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>โปรเจกต์</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr"/>
-      <c r="G25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="n">
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="19" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" s="18">
+      <c r="A26" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="B26" s="19" t="n"/>
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>OPD นรีเวช</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="n">
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="19" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1" s="18">
+      <c r="A27" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="B27" s="19" t="n"/>
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>OPD ศัลยกรรมทั่วไป</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr"/>
-      <c r="G27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="n">
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="19" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" s="18">
+      <c r="A28" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="B28" s="19" t="n"/>
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>OPD ARI</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F28" s="12" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="n">
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="19" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1" s="18">
+      <c r="A29" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="B29" s="19" t="n"/>
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>OPD เคมีบำบัด</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="n">
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="19" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1" s="18">
+      <c r="A30" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>OPD หู คอ จมูก</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="n">
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="19" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1" s="18">
+      <c r="A31" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="B31" s="19" t="n"/>
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>งานประสาทศัลยกรรม</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="n">
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="19" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1" s="18">
+      <c r="A32" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="B32" s="19" t="n"/>
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงานสูติ-นรีเวชกรรม</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="inlineStr"/>
-      <c r="G32" s="5" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="n">
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="19" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1" s="18">
+      <c r="A33" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="B33" s="19" t="n"/>
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>กลุ่มภารกิจด้านการพยาบาล</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="inlineStr"/>
-      <c r="G33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="n">
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="19" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1" s="18">
+      <c r="A34" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="B34" s="19" t="n"/>
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>งานการพยาบาลวิสัญญี</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="inlineStr"/>
-      <c r="G34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="n">
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="19" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1" s="18">
+      <c r="A35" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="B35" s="19" t="n"/>
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>งานห้องผ่าตัด</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="n">
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="19" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1" s="18">
+      <c r="A36" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="B36" s="19" t="n"/>
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>แผนกสูติ นรีเวชกรรม</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="n">
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="19" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1" s="18">
+      <c r="A37" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="B37" s="19" t="n"/>
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>แผนกศัลยกรรมหัวใจ ทรวงอก และหลอดเลือด</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="inlineStr"/>
-      <c r="G37" s="5" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="n">
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="19" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1" s="18">
+      <c r="A38" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="B38" s="19" t="n"/>
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>จ่ายกลางห้องผ่าตัด</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="n">
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="19" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1" s="18">
+      <c r="A39" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="B39" s="19" t="n"/>
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>แผนกศัลยกรรมระบบปัสสาวะ</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="inlineStr"/>
-      <c r="G39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="n">
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="19" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1" s="18">
+      <c r="A40" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="B40" s="19" t="n"/>
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>แผนกศัลยกรรมทั่วไป</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="12" t="n">
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="19" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1" s="18">
+      <c r="A41" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="B41" s="19" t="n"/>
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>แผนกศัลยกรรมกระดูก</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="n">
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="19" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1" s="18">
+      <c r="A42" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="B42" s="19" t="n"/>
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>งานทันตกรรมหยี่เต้ง</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="n">
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="19" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1" s="18">
+      <c r="A43" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="B43" s="19" t="n"/>
+      <c r="C43" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงานสังคมสงเคราะห์</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr"/>
-      <c r="G43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="n">
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="n"/>
+      <c r="G43" s="19" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1" s="18">
+      <c r="A44" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="B44" s="19" t="n"/>
+      <c r="C44" s="19" t="inlineStr">
         <is>
           <t>งานสิทธิประโยชน์</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="inlineStr"/>
-      <c r="G44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="n">
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="19" t="n"/>
+    </row>
+    <row r="45" ht="20" customHeight="1" s="18">
+      <c r="A45" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="B45" s="19" t="n"/>
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>คลังสินค้า</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="19" t="inlineStr">
         <is>
           <t>หน่วยงาน</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr"/>
-      <c r="G45" s="5" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="n"/>
+      <c r="G45" s="19" t="n"/>
+    </row>
+    <row r="47" ht="19" customHeight="1" s="18">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>รวม 44 รายการ · บัญชีวิเคราะห์ / หน่วยงาน · โมเดล account.analytic.account</t>
         </is>
@@ -2209,12 +2377,12 @@
   </sheetData>
   <autoFilter ref="A1:G45"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"ถูกต้อง,ต้องแก้ไข,ยังไม่ครบ,ข้าม"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;Lโรงพยาบาลวชิระภูเก็ต · ยืนยันข้อมูลนำเข้า ระบบงบประมาณ</oddHeader>
     <oddFooter>&amp;Lเอกสารยืนยันข้อมูลนำเข้า (Data Migration Sign-off) · ใช้ภายใน&amp;Rหน้า &amp;P / &amp;N</oddFooter>
@@ -2233,83 +2401,82 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" style="18" min="1" max="1"/>
+    <col width="42" customWidth="1" style="18" min="2" max="2"/>
+    <col width="18" customWidth="1" style="18" min="3" max="4"/>
+    <col width="14" customWidth="1" style="18" min="5" max="5"/>
+    <col width="16" customWidth="1" style="18" min="6" max="6"/>
+    <col width="28" customWidth="1" style="18" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="18">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>ชื่อแผน</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>เริ่ม</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>สิ้นสุด</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>สถานะ</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>ผลยืนยัน</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="12" t="n">
+    <row r="2" ht="20" customHeight="1" s="18">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>งบประมาณรายจ่ายประจำปี พ.ศ. 2569</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>validate</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="19" t="n"/>
+    </row>
+    <row r="4" ht="19" customHeight="1" s="18">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>รวม 1 รายการ · แผนงบประมาณประจำปี · โมเดล budget.budget</t>
         </is>
@@ -2318,12 +2485,12 @@
   </sheetData>
   <autoFilter ref="A1:G2"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="F2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"ถูกต้อง,ต้องแก้ไข,ยังไม่ครบ,ข้าม"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;Lโรงพยาบาลวชิระภูเก็ต · ยืนยันข้อมูลนำเข้า ระบบงบประมาณ</oddHeader>
     <oddFooter>&amp;Lเอกสารยืนยันข้อมูลนำเข้า (Data Migration Sign-off) · ใช้ภายใน&amp;Rหน้า &amp;P / &amp;N</oddFooter>
@@ -2342,566 +2509,566 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" style="18" min="1" max="1"/>
+    <col width="42" customWidth="1" style="18" min="2" max="2"/>
+    <col width="16" customWidth="1" style="18" min="3" max="3"/>
+    <col width="28" customWidth="1" style="18" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="18">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>ชื่อหมวด</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>ผลยืนยัน</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="12" t="n">
+    <row r="2" ht="20" customHeight="1" s="18">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์คอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr"/>
-      <c r="D2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="n">
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="19" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="18">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์งานบ้านงานครัว</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr"/>
-      <c r="D3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="19" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="18">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ยานพาหนะและขนส่ง</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="19" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="18">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์สำนักงาน</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="n">
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="19" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1" s="18">
+      <c r="A6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ไฟฟ้าและวิทยุ</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="n">
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="19" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1" s="18">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>ค่าจ้าง/ค่าเช่า/ค่าซ่อมบำรุง สิ่งก่อสร้างและครุภัณฑ์</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="19" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" s="18">
+      <c r="A8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>พักครุภัณฑ์ก่อสร้าง</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="19" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="18">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>พักปรับปรุงอาคาร</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="n">
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="19" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1" s="18">
+      <c r="A10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>หมวดครุภัณฑ์วิทยาศาสตร์และการแพทย์</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="n">
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="19" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1" s="18">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสดุการแพทย์ - การแพทย์ผ่าตัด</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="n">
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="19" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1" s="18">
+      <c r="A12" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสดุการแพทย์ - ทันตกรรม</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="n">
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="19" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1" s="18">
+      <c r="A13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสดุการแพทย์ - วัสดุการแพทย์ (ซ่อม)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="n">
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="19" t="n"/>
+    </row>
+    <row r="14" ht="40" customHeight="1" s="18">
+      <c r="A14" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสดุการแพทย์ - เอกซเรย์ (เวชภัณฑ์+intervention)</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="19" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1" s="18">
+      <c r="A15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสดุช่าง - ค่าวัสดุไฟฟ้า</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr"/>
-      <c r="D15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="19" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" s="18">
+      <c r="A16" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสดุช่าง - ค่าวัสุดก่อสร้าง</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="n">
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1" s="18">
+      <c r="A17" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสดุช่าง - ยานพาหนะ</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="n">
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="19" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" s="18">
+      <c r="A18" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสดุทั่วไป - ค่าวัสดุสำนักงาน</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="n">
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1" s="18">
+      <c r="A19" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสดุทั่วไป - งานบ้าน+น้ำดื่ม</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n">
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="19" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1" s="18">
+      <c r="A20" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสดุทั่วไป - วัสดุคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr"/>
-      <c r="D20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="n">
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1" s="18">
+      <c r="A21" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสดุทั่วไป - วัสดุโฆษณาและเผยแพร่</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="n">
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="19" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" s="18">
+      <c r="A22" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสดุทั่วไป - อื่นๆ</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="19" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1" s="18">
+      <c r="A23" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสุดวิทยาศาสตร์ - LAB - LAB (ทั่วไป)</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="n">
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="19" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1" s="18">
+      <c r="A24" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสุดวิทยาศาสตร์ - LAB - Lab (โควิด)</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="19" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" s="18">
+      <c r="A25" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสุดวิทยาศาสตร์ - ธนาคารเลือด</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="n">
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="19" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" s="18">
+      <c r="A26" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสุดวิทยาศาสตร์ - พยาธิกายวิภาค</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr"/>
-      <c r="D26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="n">
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="19" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1" s="18">
+      <c r="A27" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - วัสุดวิทยาศาสตร์ - ออกซิเจนเหลว</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr"/>
-      <c r="D27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="n">
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="19" t="n"/>
+    </row>
+    <row r="28" ht="40" customHeight="1" s="18">
+      <c r="A28" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - เครื่องแต่งกาย - เครื่องแต่งกาย (ซักฟอกและตัดเย็บ)</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="n">
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="19" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1" s="18">
+      <c r="A29" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - เชื้อเพลิง - ชื้อเพลิงรถยนต์</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="n">
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="19" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1" s="18">
+      <c r="A30" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - เชื้อเพลิง - ออกซิเจนถัง</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="n">
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="19" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1" s="18">
+      <c r="A31" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - เชื้อเพลิง - เชื้อเพลิงช่าง</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr"/>
-      <c r="D31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="n">
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="19" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1" s="18">
+      <c r="A32" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - เชื้อเพลิง - แก๊ส LPG</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr"/>
-      <c r="D32" s="5" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="n">
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="19" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1" s="18">
+      <c r="A33" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - เวชภัณฑ์ ยา - ยา + ยาเอกซเรย์</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr"/>
-      <c r="D33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="n">
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="19" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1" s="18">
+      <c r="A34" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - เวชภัณฑ์มิใช่ยา - จักษุ</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr"/>
-      <c r="D34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="n">
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="19" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1" s="18">
+      <c r="A35" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - เวชภัณฑ์มิใช่ยา - ตรวจสวนหัวใจ</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr"/>
-      <c r="D35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="n">
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="19" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1" s="18">
+      <c r="A36" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - เวชภัณฑ์มิใช่ยา - วิสัญญี</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr"/>
-      <c r="D36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="n">
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="19" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1" s="18">
+      <c r="A37" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - เวชภัณฑ์มิใช่ยา - เฝือก</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr"/>
-      <c r="D37" s="5" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="n">
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="19" t="n"/>
+    </row>
+    <row r="38" ht="40" customHeight="1" s="18">
+      <c r="A38" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - เวชภัณฑ์มิใช่ยา - เวชภัณฑ์การพยาบาล</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr"/>
-      <c r="D38" s="5" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="n">
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="19" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1" s="18">
+      <c r="A39" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - เวชภัณฑ์มิใช่ยา - เวชภัณฑ์ทั่วไป</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="n">
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="19" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1" s="18">
+      <c r="A40" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - เวชภัณฑ์มิใช่ยา - เวชภัณฑ์เภสัช</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr"/>
-      <c r="D40" s="5" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="12" t="n">
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="19" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1" s="18">
+      <c r="A41" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - เวชภัณฑ์มิใช่ยา - เวชศาสตร์ฟื้นฟู</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr"/>
-      <c r="D41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="n">
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="19" t="n"/>
+    </row>
+    <row r="42" ht="40" customHeight="1" s="18">
+      <c r="A42" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - เวชภัณฑ์มิใช่ยา - โสต ศอ นาสิก ลาริงซ์</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr"/>
-      <c r="D42" s="5" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="n">
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="19" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1" s="18">
+      <c r="A43" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - เวชภัณฑ์มิใช่ยา - ไตเทียม</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr"/>
-      <c r="D43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="n">
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="19" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1" s="18">
+      <c r="A44" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t>หมวดค่าวัสดุ - โภชนาการ - โภชนศาสตร์</t>
         </is>
       </c>
-      <c r="C44" s="12" t="inlineStr"/>
-      <c r="D44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="n">
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="19" t="n"/>
+    </row>
+    <row r="45" ht="20" customHeight="1" s="18">
+      <c r="A45" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t>โฆษณาและเผยแพร่</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr"/>
-      <c r="D45" s="5" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="19" t="n"/>
+    </row>
+    <row r="47" ht="19" customHeight="1" s="18">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>รวม 44 รายการ · หมวดงบประมาณ · โมเดล account.budget.post</t>
         </is>
@@ -2910,12 +3077,12 @@
   </sheetData>
   <autoFilter ref="A1:D45"/>
   <dataValidations count="1">
-    <dataValidation sqref="C2 C3 C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C2 C3 C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"ถูกต้อง,ต้องแก้ไข,ยังไม่ครบ,ข้าม"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;Lโรงพยาบาลวชิระภูเก็ต · ยืนยันข้อมูลนำเข้า ระบบงบประมาณ</oddHeader>
     <oddFooter>&amp;Lเอกสารยืนยันข้อมูลนำเข้า (Data Migration Sign-off) · ใช้ภายใน&amp;Rหน้า &amp;P / &amp;N</oddFooter>
@@ -2934,134 +3101,134 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" style="18" min="1" max="1"/>
+    <col width="28" customWidth="1" style="18" min="2" max="2"/>
+    <col width="70" customWidth="1" style="18" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="21" t="inlineStr">
+    <row r="2" ht="26" customHeight="1" s="18">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>วิธีตรวจก่อนลงนาม</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+    <row r="4" ht="28" customHeight="1" s="18">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>ขั้น</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>ตรวจอะไร</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>ผ่านเมื่อ</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="5" ht="36" customHeight="1" s="18">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>ประเภทข้อมูลครบตามโมดูล</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>ในชีตสรุปมีครบ Master ที่เกี่ยวข้อง และระบุโมเดล/คีย์จับคู่</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="6" ht="36" customHeight="1" s="18">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>จำนวน record</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>จำนวนในระบบตรงกับไฟล์ต้นทางที่หน่วยงานส่ง (กรอกคอลัมน์จำนวนต้นทาง แล้วดูผลต่าง = 0)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="7" ht="36" customHeight="1" s="18">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>รายการตัวอย่าง</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>สุ่มตรวจรหัสและชื่อในชีตยืนยัน ไม่สลับ ไม่ซ้ำ ไม่สะกดผิดจนใช้ไม่ได้</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="8" ht="36" customHeight="1" s="18">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>ความสัมพันธ์ข้ามโมดูล</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>เช่น สินค้ามีหมวดและหน่วยนับ · ผู้ขายถูกใช้ตั้งเจ้าหนี้ได้ · แหล่งเงินถูกใช้ในแผนงบ</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="9" ht="36" customHeight="1" s="18">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>ข้อมูลคงค้าง</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>ตรวจชีต PO คงค้าง, เจ้าหนี้คงค้าง, TB ปีงบ 2569 (1 ต.ค. 2568–30 ก.ย. 2569) ถ้าเป็น 0 ให้ยืนยันว่ายังไม่นำเข้า</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="10" ht="36" customHeight="1" s="18">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>ลงนาม</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>เจ้าของข้อมูล + IT ลงนามในปก และกรอกผลยืนยันรายประเภทในสรุป</t>
         </is>
@@ -3072,7 +3239,7 @@
     <mergeCell ref="B2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
   <headerFooter>
     <oddHeader>&amp;Lโรงพยาบาลวชิระภูเก็ต · ยืนยันข้อมูลนำเข้า ระบบงบประมาณ</oddHeader>
     <oddFooter>&amp;Lเอกสารยืนยันข้อมูลนำเข้า (Data Migration Sign-off) · ใช้ภายใน&amp;Rหน้า &amp;P / &amp;N</oddFooter>
@@ -3090,854 +3257,994 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" style="18" min="1" max="1"/>
+    <col width="32" customWidth="1" style="18" min="2" max="2"/>
+    <col width="62" customWidth="1" style="18" min="3" max="3"/>
+    <col width="28" customWidth="1" style="18" min="4" max="4"/>
+    <col width="36" customWidth="1" style="18" min="5" max="5"/>
+    <col width="22" customWidth="1" style="18" min="6" max="6"/>
+    <col width="14" customWidth="1" style="18" min="7" max="7"/>
+    <col width="22" customWidth="1" style="18" min="8" max="8"/>
+    <col width="24" customWidth="1" style="18" min="9" max="9"/>
+    <col width="16" customWidth="1" style="18" min="10" max="10"/>
+    <col width="12" customWidth="1" style="18" min="11" max="11"/>
+    <col width="16" customWidth="1" style="18" min="12" max="13"/>
+    <col width="14" customWidth="1" style="18" min="14" max="15"/>
+    <col width="28" customWidth="1" style="18" min="16" max="16"/>
+    <col width="62" customWidth="1" style="18" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="18">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>ประเภทข้อมูล</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>ข้อมูลนี้คืออะไร / ใช้ทำอะไรในระบบ</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>กลุ่ม</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>โมดูลที่เกี่ยวข้อง</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>โมเดลในระบบ</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>คีย์จับคู่</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>จำนวนในระบบ</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>สถานะนำเข้า</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>ชีตรายการยืนยัน</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>จำนวนต้นทาง (กรอก)</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>ผลต่าง</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>ผลยืนยัน</t>
         </is>
       </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>ผู้ยืนยัน</t>
         </is>
       </c>
-      <c r="N1" s="11" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>ลงชื่อ</t>
         </is>
       </c>
-      <c r="O1" s="11" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>วันที่</t>
         </is>
       </c>
-      <c r="P1" s="11" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="12" t="n">
+      <c r="R1" s="32" t="inlineStr">
+        <is>
+          <t>อ้างอิงการได้มาของข้อมูล</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="78" customHeight="1" s="18">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>แหล่งเงิน</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>คือที่มาของเงิน เช่น เงินงบประมาณ เงินบำรุง เงิน UC เงินบริจาค ใช้เลือกตอนหน่วยงานขอตั้งงบและตอนขอซื้อ (PR) เพื่อให้ระบบจับคู่วงเงินถูกแหล่ง ใช้ข้ามแหล่งเงินไม่ได้</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>งบประมาณ</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr">
         <is>
           <t>vpk.budget.fund.source</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="19" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="G2" s="13" t="n">
+      <c r="H2" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>นำเข้าแล้ว</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="J2" s="19" t="inlineStr">
         <is>
           <t>ยืนยัน-แหล่งเงิน</t>
         </is>
       </c>
-      <c r="J2" s="13" t="inlineStr"/>
-      <c r="K2" s="13">
-        <f>IF(J2="","",G2-J2)</f>
+      <c r="K2" s="8" t="n"/>
+      <c r="L2" s="8">
+        <f>IF(K2="","",H2-K2)</f>
         <v/>
       </c>
-      <c r="L2" s="12" t="inlineStr"/>
-      <c r="M2" s="5" t="inlineStr"/>
-      <c r="N2" s="5" t="inlineStr"/>
-      <c r="O2" s="12" t="inlineStr"/>
-      <c r="P2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="12" t="n">
+      <c r="M2" s="7" t="n"/>
+      <c r="N2" s="19" t="n"/>
+      <c r="O2" s="19" t="n"/>
+      <c r="P2" s="7" t="n"/>
+      <c r="Q2" s="19" t="n"/>
+      <c r="R2" s="33" t="inlineStr">
+        <is>
+          <t>ข้อมูลตั้งต้นของโมดูล ติดตั้งจาก vpk_budget/data/budget_fund_source_data.xml ครบ 20 รายการ (รหัส STATE_BUDGET ถึง WELFARE) รายชื่อแหล่งเงินของโรงพยาบาลบันทึกไว้ในไฟล์แม่แบบ 05_UAT_นำเข้าข้อมูล_Master/vpk_budget_master_template_เพิ่มเติม.xlsx ชีต FundSource</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="78" customHeight="1" s="18">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>กลุ่มงบประมาณ-วัสดุ</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>คือกลุ่มวัสดุสำหรับจัดซื้อ เช่น ยา เวชภัณฑ์มิใช่ยา วัสดุการแพทย์ วัสดุวิทยาศาสตร์ ใช้ตอนตั้งงบวัสดุและตอนขอซื้อวัสดุ เพื่อจับคู่บรรทัดวงเงินของกลุ่มนั้น</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>งบประมาณ</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>vpk.budget.group</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="G3" s="13" t="n">
+      <c r="H3" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="H3" s="14" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>นำเข้าแล้ว</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>ยืนยัน-กลุ่มงบ</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr"/>
-      <c r="K3" s="13">
-        <f>IF(J3="","",G3-J3)</f>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8">
+        <f>IF(K3="","",H3-K3)</f>
         <v/>
       </c>
-      <c r="L3" s="12" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr"/>
-      <c r="O3" s="12" t="inlineStr"/>
-      <c r="P3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="12" t="n">
+      <c r="M3" s="7" t="n"/>
+      <c r="N3" s="19" t="n"/>
+      <c r="O3" s="19" t="n"/>
+      <c r="P3" s="7" t="n"/>
+      <c r="Q3" s="19" t="n"/>
+      <c r="R3" s="33" t="inlineStr">
+        <is>
+          <t>รหัส 9 กลุ่มมาจากข้อมูลตั้งต้น vpk_budget/data/budget_group_data.xml ชื่อที่ใช้อยู่ปรับตามชีต BudgetGroup-supplies ใน 05_UAT_นำเข้าข้อมูล_Master/vpk_budget_master_template.xlsx ผ่านเมนูนำเข้าข้อมูลหลัก (เช่น TECHNICIAN จาก “ช่าง” เป็น “วัสดุช่าง”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="78" customHeight="1" s="18">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>ประเภทวัสดุย่อย</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>คือรายละเอียดภายใต้กลุ่มงบวัสดุ เช่น ยา เฝือก เวชภัณฑ์การพยาบาล ใช้แยกรายการในแบบฟอร์มตั้งงบวัสดุ และผูกกับกลุ่มงบตอนขอซื้อ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>งบประมาณ</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>vpk.budget.material.sub.type</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>code + กลุ่มงบ</t>
         </is>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="H4" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>นำเข้าแล้ว</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>ยืนยัน-วัสดุย่อย</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr"/>
-      <c r="K4" s="13">
-        <f>IF(J4="","",G4-J4)</f>
+      <c r="K4" s="8" t="n"/>
+      <c r="L4" s="8">
+        <f>IF(K4="","",H4-K4)</f>
         <v/>
       </c>
-      <c r="L4" s="12" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="12" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="12" t="n">
+      <c r="M4" s="7" t="n"/>
+      <c r="N4" s="19" t="n"/>
+      <c r="O4" s="19" t="n"/>
+      <c r="P4" s="7" t="n"/>
+      <c r="Q4" s="19" t="n"/>
+      <c r="R4" s="33" t="inlineStr">
+        <is>
+          <t>ไม่มีข้อมูลตั้งต้นในโมดูล นำเข้าผ่านเมนูนำเข้าข้อมูลหลัก จากชีต MaterialSubType ใน 05_UAT_นำเข้าข้อมูล_Master/vpk_budget_master_template.xlsx รายการเชื้อเพลิงเพิ่มจากไฟล์ vpk_budget_master_template_เพิ่มเติม.xlsx ชีต MaterialSubType ชื่อหมวดถอดจากแบบตั้งงบวัสดุที่งานงบประมาณใช้</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1" s="18">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>ประเภทงบประมาณ</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>คือประเภทหลักของงบ ได้แก่ วัสดุ ครุภัณฑ์ ก่อสร้าง โครงการ ใช้กำหนดว่าคำของบและวงเงินอยู่กลุ่มใด และผูกกับแบบฟอร์มคำของบ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>งบประมาณ</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>vpk.budget.type</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="H5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>นำเข้าแล้ว</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="19" t="inlineStr">
         <is>
           <t>ยืนยัน-ประเภทงบ</t>
         </is>
       </c>
-      <c r="J5" s="13" t="inlineStr"/>
-      <c r="K5" s="13">
-        <f>IF(J5="","",G5-J5)</f>
+      <c r="K5" s="8" t="n"/>
+      <c r="L5" s="8">
+        <f>IF(K5="","",H5-K5)</f>
         <v/>
       </c>
-      <c r="L5" s="12" t="inlineStr"/>
-      <c r="M5" s="5" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr"/>
-      <c r="O5" s="12" t="inlineStr"/>
-      <c r="P5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="12" t="n">
+      <c r="M5" s="7" t="n"/>
+      <c r="N5" s="19" t="n"/>
+      <c r="O5" s="19" t="n"/>
+      <c r="P5" s="7" t="n"/>
+      <c r="Q5" s="19" t="n"/>
+      <c r="R5" s="33" t="inlineStr">
+        <is>
+          <t>ข้อมูลตั้งต้นของโมดูล จาก vpk_budget/data/budget_type_data.xml จำนวน 4 ประเภท ได้แก่ วัสดุ ครุภัณฑ์ ก่อสร้าง โครงการ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1" s="18">
+      <c r="A6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>กลุ่มครุภัณฑ์</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>คือกลุ่มครุภัณฑ์ เช่น ครุภัณฑ์การแพทย์ ครุภัณฑ์ไฟฟ้า ใช้ตอนตั้งงบครุภัณฑ์ และผูกกับหมวดสินค้าเพื่อให้ขอซื้อครุภัณฑ์เข้ากลุ่มที่ถูกต้อง</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>งบประมาณ</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>vpk.budget.asset.category</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>นำเข้าแล้ว</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="19" t="inlineStr">
         <is>
           <t>ยืนยัน-กลุ่มครุภัณฑ์</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr"/>
-      <c r="K6" s="13">
-        <f>IF(J6="","",G6-J6)</f>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8">
+        <f>IF(K6="","",H6-K6)</f>
         <v/>
       </c>
-      <c r="L6" s="12" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="12" t="n">
+      <c r="M6" s="7" t="n"/>
+      <c r="N6" s="19" t="n"/>
+      <c r="O6" s="19" t="n"/>
+      <c r="P6" s="7" t="n"/>
+      <c r="Q6" s="19" t="n"/>
+      <c r="R6" s="33" t="inlineStr">
+        <is>
+          <t>6 รายการตั้งต้นจาก vpk_budget/data/budget_asset_category_data.xml (office, vehicle, computer, workshop, medical, other) แล้วเพิ่มรหัส EQ01–EQ09 และผูกหมวดสินค้าตามชีต AssetCategory ใน 05_UAT_นำเข้าข้อมูล_Master/vpk_budget_master_template_เพิ่มเติม.xlsx รายการ vehicle และ other ถูกปิดการใช้งาน</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="78" customHeight="1" s="18">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>แบบฟอร์มคำของบ</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>คือชนิดแบบฟอร์มที่หน่วยงานใช้ขอตั้งงบ เช่น แบบฟอร์มตั้งงบวัสดุ แบบฟอร์มครุภัณฑ์ ใช้เปิดหน้าคำของบให้กรอกตามประเภทงาน</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>งบประมาณ</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>vpk.budget.request.form.type</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>นำเข้าแล้ว</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>ยืนยัน-แบบฟอร์ม</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr"/>
-      <c r="K7" s="13">
-        <f>IF(J7="","",G7-J7)</f>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8">
+        <f>IF(K7="","",H7-K7)</f>
         <v/>
       </c>
-      <c r="L7" s="12" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr"/>
-      <c r="P7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="12" t="n">
+      <c r="M7" s="7" t="n"/>
+      <c r="N7" s="19" t="n"/>
+      <c r="O7" s="19" t="n"/>
+      <c r="P7" s="7" t="n"/>
+      <c r="Q7" s="19" t="n"/>
+      <c r="R7" s="33" t="inlineStr">
+        <is>
+          <t>ข้อมูลตั้งต้นของโมดูล จาก vpk_budget/data/budget_request_form_type_data.xml จำนวน 4 แบบฟอร์ม ตามแบบที่งานงบประมาณใช้ (ตั้งงบวัสดุ ครุภัณฑ์ ก่อสร้าง โครงการ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="78" customHeight="1" s="18">
+      <c r="A8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>ประเภทงบในแบบฟอร์ม</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>คือการผูกว่าแบบฟอร์มแต่ละใบใช้ประเภทงบใด ใช้ให้ระบบเปิดแท็บและตรวจวงเงินให้ตรงประเภทงบของแบบฟอร์มนั้น</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>งบประมาณ</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>vpk.budget.request.form.type.line</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>form + ประเภทงบ</t>
         </is>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>นำเข้าแล้ว</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="19" t="inlineStr">
         <is>
           <t>ยืนยัน-แท็บแบบฟอร์ม</t>
         </is>
       </c>
-      <c r="J8" s="13" t="inlineStr"/>
-      <c r="K8" s="13">
-        <f>IF(J8="","",G8-J8)</f>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8">
+        <f>IF(K8="","",H8-K8)</f>
         <v/>
       </c>
-      <c r="L8" s="12" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="5" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr"/>
-      <c r="P8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="12" t="n">
+      <c r="M8" s="7" t="n"/>
+      <c r="N8" s="19" t="n"/>
+      <c r="O8" s="19" t="n"/>
+      <c r="P8" s="7" t="n"/>
+      <c r="Q8" s="19" t="n"/>
+      <c r="R8" s="33" t="inlineStr">
+        <is>
+          <t>สร้างอัตโนมัติตอนติดตั้งโมดูล จาก vpk_budget/data/budget_request_form_type_line_data.xml ผูกหนึ่งแบบฟอร์มต่อหนึ่งประเภทงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="78" customHeight="1" s="18">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>แผนวิเคราะห์ / มิติหน่วยงาน</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>คือมิติที่ใช้แยกตัวเลข เช่น หน่วยงานและโปรเจกต์ ใช้เป็นโครงสร้างของบัญชีวิเคราะห์ ให้งบประมาณ จัดซื้อ และบัญชีอ้างหน่วยงานชุดเดียวกัน</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>งบประมาณ, บัญชี</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>account.analytic.plan</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>นำเข้าแล้ว</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t>ยืนยัน-แผนวิเคราะห์</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr"/>
-      <c r="K9" s="13">
-        <f>IF(J9="","",G9-J9)</f>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="8">
+        <f>IF(K9="","",H9-K9)</f>
         <v/>
       </c>
-      <c r="L9" s="12" t="inlineStr"/>
-      <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr"/>
-      <c r="P9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="12" t="n">
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="19" t="n"/>
+      <c r="O9" s="19" t="n"/>
+      <c r="P9" s="7" t="n"/>
+      <c r="Q9" s="19" t="n"/>
+      <c r="R9" s="33" t="inlineStr">
+        <is>
+          <t>สร้างในระบบบัญชีวิเคราะห์ ไม่ได้มาจากไฟล์นำเข้าในชุด UAT แผน “โปรเจกต์” เป็นแผนมาตรฐานของ Odoo ที่ปรับชื่อเป็นภาษาไทย แผน “หน่วยงาน” และแผนงานเภสัชกรรมสร้างเพิ่มระหว่างเตรียมข้อมูล</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="78" customHeight="1" s="18">
+      <c r="A10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>บัญชีวิเคราะห์ / หน่วยงาน</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>คือหน่วยงานหรือโครงการที่ถือวงเงิน ใช้ใส่ในแผนงบ คำของบ และใบขอซื้อ เพื่อกันเงินและตัดงบรายหน่วยงาน</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>งบประมาณ, จัดซื้อ, บัญชี</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>account.analytic.account</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>นำเข้าแล้ว</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="19" t="inlineStr">
         <is>
           <t>ยืนยัน-หน่วยงานวิเคราะห์</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr"/>
-      <c r="K10" s="13">
-        <f>IF(J10="","",G10-J10)</f>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8">
+        <f>IF(K10="","",H10-K10)</f>
         <v/>
       </c>
-      <c r="L10" s="12" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr"/>
-      <c r="N10" s="5" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr"/>
-      <c r="P10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="12" t="n">
+      <c r="M10" s="7" t="n"/>
+      <c r="N10" s="19" t="n"/>
+      <c r="O10" s="19" t="n"/>
+      <c r="P10" s="7" t="n"/>
+      <c r="Q10" s="19" t="n"/>
+      <c r="R10" s="33" t="inlineStr">
+        <is>
+          <t>สร้างในระบบบัญชีวิเคราะห์ระหว่างเตรียม UAT ไม่ได้มาจากไฟล์แม่แบบในชุดเอกสารนี้ มีรายการทดสอบ PED-001, RAD-001 และ UAT-DEPT หน่วยงานที่เหลือกรอกชื่อในระบบ และส่วนใหญ่ยังไม่มีรหัส</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="78" customHeight="1" s="18">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>แผนงบประมาณประจำปี</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>คือแผนวงเงินของปีงบประมาณ พร้อมวันเริ่มและวันสิ้นสุด ใช้เป็นกรอบที่บรรทัดวงเงินและคำของบของปีนั้นอ้างอิง</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>งบประมาณ</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>budget.budget</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>name + ช่วงวันที่</t>
         </is>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>นำเข้าแล้ว</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr">
         <is>
           <t>ยืนยัน-แผนปี</t>
         </is>
       </c>
-      <c r="J11" s="13" t="inlineStr"/>
-      <c r="K11" s="13">
-        <f>IF(J11="","",G11-J11)</f>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8">
+        <f>IF(K11="","",H11-K11)</f>
         <v/>
       </c>
-      <c r="L11" s="12" t="inlineStr"/>
-      <c r="M11" s="5" t="inlineStr"/>
-      <c r="N11" s="5" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr"/>
-      <c r="P11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="12" t="n">
+      <c r="M11" s="7" t="n"/>
+      <c r="N11" s="19" t="n"/>
+      <c r="O11" s="19" t="n"/>
+      <c r="P11" s="7" t="n"/>
+      <c r="Q11" s="19" t="n"/>
+      <c r="R11" s="33" t="inlineStr">
+        <is>
+          <t>สร้างในเมนูแผนงบประมาณ ไม่ได้มาจากไฟล์ ชื่อ “งบประมาณรายจ่ายประจำปี พ.ศ. 2569” วันที่ 1 ม.ค. 2569 ถึง 31 ธ.ค. 2569 สถานะอนุมัติ (validate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="78" customHeight="1" s="18">
+      <c r="A12" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>หมวดงบประมาณ</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>คือหมวดที่ใช้ควบคุมวงเงิน เช่น ครุภัณฑ์คอมพิวเตอร์ ครุภัณฑ์สำนักงาน ใช้จับคู่ตอนเช็คงบและกันเงินในใบขอซื้อกับบรรทัดวงเงิน</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>งบประมาณ, จัดซื้อ</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>account.budget.post</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>นำเข้าแล้ว</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="19" t="inlineStr">
         <is>
           <t>ยืนยัน-หมวดงบ</t>
         </is>
       </c>
-      <c r="J12" s="13" t="inlineStr"/>
-      <c r="K12" s="13">
-        <f>IF(J12="","",G12-J12)</f>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8">
+        <f>IF(K12="","",H12-K12)</f>
         <v/>
       </c>
-      <c r="L12" s="12" t="inlineStr"/>
-      <c r="M12" s="5" t="inlineStr"/>
-      <c r="N12" s="5" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr"/>
-      <c r="P12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="12" t="n">
+      <c r="M12" s="7" t="n"/>
+      <c r="N12" s="19" t="n"/>
+      <c r="O12" s="19" t="n"/>
+      <c r="P12" s="7" t="n"/>
+      <c r="Q12" s="19" t="n"/>
+      <c r="R12" s="33" t="inlineStr">
+        <is>
+          <t>สร้างในระบบจากชื่อหมวดที่ใช้กับคำของบและแผนงบ ไม่ได้มาจากไฟล์ XML ชื่อหมวดวัสดุอิงประเภทวัสดุย่อย ชื่อหมวดครุภัณฑ์อิงกลุ่มครุภัณฑ์</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="78" customHeight="1" s="18">
+      <c r="A13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>บรรทัดวงเงินงบประมาณ</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>คือยอดเงินที่ตั้งไว้ แยกตามแผน หมวด หน่วยงาน และแหล่งเงิน ใช้เป็นเพดานให้ระบบตรวจว่างบพอหรือไม่ตอนขอซื้อ ชุดนี้ยังไม่นำเข้า</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>ตั้งค่า</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>งบประมาณ</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>budget.lines</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>แผน + หมวด + หน่วยงาน</t>
         </is>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>ยังไม่นำเข้า</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="13" t="inlineStr"/>
-      <c r="K13" s="13">
-        <f>IF(J13="","",G13-J13)</f>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8">
+        <f>IF(K13="","",H13-K13)</f>
         <v/>
       </c>
-      <c r="L13" s="12" t="inlineStr"/>
-      <c r="M13" s="5" t="inlineStr"/>
-      <c r="N13" s="5" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr"/>
-      <c r="P13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="12" t="n">
+      <c r="M13" s="7" t="n"/>
+      <c r="N13" s="19" t="n"/>
+      <c r="O13" s="19" t="n"/>
+      <c r="P13" s="7" t="n"/>
+      <c r="Q13" s="19" t="n"/>
+      <c r="R13" s="33" t="inlineStr">
+        <is>
+          <t>ยังไม่นำเข้า ยังไม่มีการตั้งวงเงินรายแผน หมวด หน่วยงาน และแหล่งเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="78" customHeight="1" s="18">
+      <c r="A14" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>คำของบหน่วยงาน</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>คือเอกสารที่หน่วยงานกรอกเพื่อขอตั้งงบประจำปี ใช้รวบรวมความต้องการก่อนจัดสรรวงเงินลงแผน เป็นเอกสารทำงาน ไม่ใช่ข้อมูลหลักสำหรับนำเข้า</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>ธุรกรรม</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>งบประมาณ</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>departmental.budget.request</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>เลขที่เอกสาร</t>
         </is>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>มีข้อมูลในระบบ (ธุรกรรม)</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="13" t="inlineStr"/>
-      <c r="K14" s="13">
-        <f>IF(J14="","",G14-J14)</f>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8">
+        <f>IF(K14="","",H14-K14)</f>
         <v/>
       </c>
-      <c r="L14" s="12" t="inlineStr"/>
-      <c r="M14" s="5" t="inlineStr"/>
-      <c r="N14" s="5" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr"/>
-      <c r="P14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="M14" s="7" t="n"/>
+      <c r="N14" s="19" t="n"/>
+      <c r="O14" s="19" t="n"/>
+      <c r="P14" s="7" t="n"/>
+      <c r="Q14" s="19" t="n"/>
+      <c r="R14" s="33" t="inlineStr">
+        <is>
+          <t>มี 2 เอกสารในระบบ เป็นธุรกรรมที่กรอกในหน้าคำของบหน่วยงาน ไม่ใช่ข้อมูลหลักที่นำเข้าจากไฟล์</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="21" customHeight="1" s="18">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>รวมจำนวนทุกประเภทในชีตนี้</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr"/>
-      <c r="D15" s="18" t="inlineStr"/>
-      <c r="E15" s="18" t="inlineStr"/>
-      <c r="F15" s="18" t="inlineStr"/>
-      <c r="G15" s="19">
-        <f>SUM(G2:G14)</f>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="14">
+        <f>SUM(H2:H14)</f>
         <v/>
       </c>
-      <c r="H15" s="18" t="inlineStr"/>
-      <c r="I15" s="18" t="inlineStr"/>
-      <c r="J15" s="18" t="inlineStr"/>
-      <c r="K15" s="18" t="inlineStr"/>
-      <c r="L15" s="18" t="inlineStr"/>
-      <c r="M15" s="18" t="inlineStr"/>
-      <c r="N15" s="18" t="inlineStr"/>
-      <c r="O15" s="18" t="inlineStr"/>
-      <c r="P15" s="18" t="inlineStr"/>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13" t="n"/>
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="13" t="n"/>
+      <c r="M15" s="13" t="n"/>
+      <c r="N15" s="13" t="n"/>
+      <c r="O15" s="13" t="n"/>
+      <c r="P15" s="13" t="n"/>
+      <c r="Q15" s="13" t="n"/>
+      <c r="R15" s="34" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>ข้อมูล ณ 30 ส.ค. 2569  23:24 จากฐาน VPK-S1  คอลัมน์ “จำนวนต้นทาง” ให้เจ้าของข้อมูลกรอกจากไฟล์ที่ส่งมา ถ้าผลต่าง ≠ 0 ให้เลือกผลยืนยันเป็น ต้องแก้ไข หรือ ยังไม่ครบ  กลุ่ม Master = ข้อมูลหลักที่ใช้ทั้งระบบ · ตั้งค่า = วงเงิน/ค่าคงที่ · ธุรกรรม = เอกสารปฏิบัติงาน · คงค้าง = PO ค้างรับ/ค้างตั้งหนี้, เจ้าหนี้ค้างจ่าย, งบทดลอง TB ปี 2569 (ปีงบประมาณ 1 ต.ค. 2568 – 30 ก.ย. 2569)</t>
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>ข้อมูล ณ 30 ส.ค. 2569  23:24 จากฐาน VPK-S1  คอลัมน์ “จำนวนต้นทาง” ให้เจ้าของข้อมูลกรอกจากไฟล์ที่ส่งมา ถ้าผลต่าง ≠ 0 ให้เลือกผลยืนยันเป็น ต้องแก้ไข หรือ ยังไม่ครบ  กลุ่ม Master = ข้อมูลหลักที่ใช้ทั้งระบบ · ตั้งค่า = วงเงิน/ค่าคงที่ · ธุรกรรม = เอกสารปฏิบัติงาน · คงค้าง = PO ค้างรับ/ค้างตั้งหนี้, เจ้าหนี้ค้างจ่าย, งบทดลอง TB ปี 2569 (ปีงบประมาณ 1 ต.ค. 2568 – 30 ก.ย. 2569)  คอลัมน์ “อ้างอิงการได้มาของข้อมูล” บันทึกว่าแต่ละประเภทได้มาจากข้อมูลตั้งต้นของโมดูล ไฟล์แม่แบบที่นำเข้า หรือสร้างในระบบ</t>
         </is>
       </c>
     </row>
     <row r="18"/>
     <row r="19"/>
   </sheetData>
-  <autoFilter ref="A1:P14"/>
+  <autoFilter ref="A1:R14"/>
   <mergeCells count="1">
-    <mergeCell ref="A17:P19"/>
+    <mergeCell ref="A17:R19"/>
   </mergeCells>
   <conditionalFormatting sqref="L2:L14">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"ถูกต้อง"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
       <formula>"ต้องแก้ไข"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
       <formula>"ยังไม่ครบ"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"ถูกต้อง,ต้องแก้ไข,ยังไม่ครบ,ข้าม"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;Lโรงพยาบาลวชิระภูเก็ต · ยืนยันข้อมูลนำเข้า ระบบงบประมาณ</oddHeader>
     <oddFooter>&amp;Lเอกสารยืนยันข้อมูลนำเข้า (Data Migration Sign-off) · ใช้ภายใน&amp;Rหน้า &amp;P / &amp;N</oddFooter>
@@ -3956,556 +4263,555 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" style="18" min="1" max="1"/>
+    <col width="18" customWidth="1" style="18" min="2" max="3"/>
+    <col width="42" customWidth="1" style="18" min="4" max="4"/>
+    <col width="14" customWidth="1" style="18" min="5" max="5"/>
+    <col width="16" customWidth="1" style="18" min="6" max="6"/>
+    <col width="28" customWidth="1" style="18" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="18">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>รหัส</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>ชื่อ</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>สถานะ</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>ผลยืนยัน</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="12" t="n">
+    <row r="2" ht="20" customHeight="1" s="18">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>STATE_BUDGET</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>เงินงบประมาณ</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="n">
+      <c r="E2" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="19" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="18">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>HOSP_MAINT</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>เงินบำรุง</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="19" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="18">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="19" t="n">
         <v>21</v>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>UC_FUND</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>เงินกองทุนหลักประกันสุขภาพ (UC)</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="19" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="18">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="19" t="n">
         <v>22</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>DONATION</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>เงินบริจาค</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="n">
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="19" t="n"/>
+    </row>
+    <row r="6" ht="40" customHeight="1" s="18">
+      <c r="A6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="19" t="n">
         <v>23</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>DONATION_OBJECTIVE</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>ระบุวัตถุประสงค์</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="n">
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="19" t="n"/>
+    </row>
+    <row r="7" ht="40" customHeight="1" s="18">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>DONATION_LUANPORCHAM</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>หลวงพ่อแช่ม</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="19" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" s="18">
+      <c r="A8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>DONATION_Other</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>อื่นๆ ระบุ (ROTARY , LOINS ,Fund raise )</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="19" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="18">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="19" t="n">
         <v>26</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>CAPITAL</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>งบลงทุน</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="n">
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="19" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1" s="18">
+      <c r="A10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="19" t="n">
         <v>27</v>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>DEPR</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>งบค่าเสื่อม</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="n">
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="19" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1" s="18">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="19" t="n">
         <v>28</v>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>PAO</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>งบอบจ</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="n">
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="19" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1" s="18">
+      <c r="A12" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="19" t="n">
         <v>29</v>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>SSO</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>งบ 2.5% ปกส.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="n">
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="19" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1" s="18">
+      <c r="A13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>MIGRANT</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>งบแรงงานต่างด้าว</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="n">
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="19" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1" s="18">
+      <c r="A14" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="19" t="n">
         <v>31</v>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>PROV</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>งบพัฒนาจังหวัด</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="19" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1" s="18">
+      <c r="A15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="19" t="n">
         <v>32</v>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>ANDAMAN</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>งบพัฒนากลุ่มจังหวัดภาคใต้ฝั่งอันดามัน</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="19" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" s="18">
+      <c r="A16" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="19" t="n">
         <v>33</v>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>LOTTERY</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>งบสนับสนุนโครงการสลากการกุศล</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="n">
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1" s="18">
+      <c r="A17" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="19" t="n">
         <v>34</v>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>PAO-HF</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>งบอบจ (กองทุนส่งเสริมและฟื้นฟูสุขภาพ)</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="n">
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="19" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" s="18">
+      <c r="A18" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="19" t="n">
         <v>35</v>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>MED-EDU</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>หมวดอุดหนุนศูนย์แพทยศาสตร</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="n">
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1" s="18">
+      <c r="A19" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="19" t="n">
         <v>36</v>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>LTC-LOCAL</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>กองทุนหลักประกันสุขภาพเทศบาลนครภูเก็ต</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n">
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="19" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1" s="18">
+      <c r="A20" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="19" t="n">
         <v>37</v>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>ACADEMIC</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>เงินสนับสนุนประชุมวิชาการ</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="n">
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1" s="18">
+      <c r="A21" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="19" t="n">
         <v>38</v>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>WELFARE</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>เงินสวัสดิการ</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="19" t="n"/>
+    </row>
+    <row r="23" ht="19" customHeight="1" s="18">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>รวม 20 รายการ · แหล่งเงิน · โมเดล vpk.budget.fund.source</t>
         </is>
@@ -4514,12 +4820,12 @@
   </sheetData>
   <autoFilter ref="A1:G21"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"ถูกต้อง,ต้องแก้ไข,ยังไม่ครบ,ข้าม"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;Lโรงพยาบาลวชิระภูเก็ต · ยืนยันข้อมูลนำเข้า ระบบงบประมาณ</oddHeader>
     <oddFooter>&amp;Lเอกสารยืนยันข้อมูลนำเข้า (Data Migration Sign-off) · ใช้ภายใน&amp;Rหน้า &amp;P / &amp;N</oddFooter>
@@ -4538,281 +4844,282 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" style="28" min="1" max="1"/>
+    <col width="18" customWidth="1" style="28" min="2" max="2"/>
+    <col width="23.1640625" customWidth="1" style="28" min="3" max="3"/>
+    <col width="42" customWidth="1" style="28" min="4" max="4"/>
+    <col width="11.1640625" bestFit="1" customWidth="1" style="28" min="5" max="5"/>
+    <col width="16" customWidth="1" style="28" min="6" max="6"/>
+    <col width="28" customWidth="1" style="28" min="7" max="7"/>
+    <col width="8.83203125" customWidth="1" style="28" min="8" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="18">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="27" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="27" t="inlineStr">
         <is>
           <t>รหัส</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="27" t="inlineStr">
         <is>
           <t>ชื่อ</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="27" t="inlineStr">
         <is>
           <t>สถานะ</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="27" t="inlineStr">
         <is>
           <t>ผลยืนยัน</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="27" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="12" t="n">
+    <row r="2" ht="20" customHeight="1" s="18">
+      <c r="A2" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="30" t="inlineStr">
         <is>
           <t>MEDICINE</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="30" t="inlineStr">
         <is>
           <t>เวชภัณฑ์ ยา</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="n">
+      <c r="E2" s="30" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F2" s="29" t="n"/>
+      <c r="G2" s="30" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="18">
+      <c r="A3" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="30" t="inlineStr">
         <is>
           <t>NON_MEDICINE</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="30" t="inlineStr">
         <is>
           <t>เวชภัณฑ์มิใช่ยา</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="E3" s="30" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F3" s="29" t="n"/>
+      <c r="G3" s="30" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="18">
+      <c r="A4" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>MEDICAL_SUPPLY</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>วัสดุการแพทย์</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F4" s="29" t="n"/>
+      <c r="G4" s="30" t="n"/>
+    </row>
+    <row r="5" ht="40" customHeight="1" s="18">
+      <c r="A5" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t>SCIENTIFIC_SUPPLY</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>วัสดุวิทยาศาสตร์</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="n">
+      <c r="E5" s="30" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="30" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1" s="18">
+      <c r="A6" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>GENERAL_SUPPLY</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>วัสดุทั่วไป</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="n">
+      <c r="E6" s="30" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F6" s="29" t="n"/>
+      <c r="G6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1" s="18">
+      <c r="A7" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>FUEL</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>เชื้อเพลิง</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="E7" s="30" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F7" s="29" t="n"/>
+      <c r="G7" s="30" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" s="18">
+      <c r="A8" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="30" t="n">
         <v>70</v>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>TECHNICIAN</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>วัสดุช่าง</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="30" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="18">
+      <c r="A9" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>NUTRITION</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>โภชนาการ</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="n">
+      <c r="E9" s="30" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="30" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1" s="18">
+      <c r="A10" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="30" t="n">
         <v>90</v>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>UNIFORM</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>เครื่องแต่งกาย</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F10" s="29" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>รวม 9 รายการ · กลุ่มงบประมาณ-วัสดุ · โมเดล vpk.budget.group</t>
         </is>
@@ -4821,12 +5128,12 @@
   </sheetData>
   <autoFilter ref="A1:G10"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"ถูกต้อง,ต้องแก้ไข,ยังไม่ครบ,ข้าม"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;Lโรงพยาบาลวชิระภูเก็ต · ยืนยันข้อมูลนำเข้า ระบบงบประมาณ</oddHeader>
     <oddFooter>&amp;Lเอกสารยืนยันข้อมูลนำเข้า (Data Migration Sign-off) · ใช้ภายใน&amp;Rหน้า &amp;P / &amp;N</oddFooter>
@@ -4845,1293 +5152,1291 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" style="18" min="1" max="1"/>
+    <col width="18" customWidth="1" style="18" min="2" max="3"/>
+    <col width="42" customWidth="1" style="18" min="4" max="4"/>
+    <col width="18" customWidth="1" style="18" min="5" max="6"/>
+    <col width="14" customWidth="1" style="18" min="7" max="7"/>
+    <col width="16" customWidth="1" style="18" min="8" max="8"/>
+    <col width="28" customWidth="1" style="18" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="18">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>รหัส</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>ชื่อ</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>รหัสกลุ่มงบ</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>กลุ่มงบ</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>สถานะ</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>ผลยืนยัน</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="12" t="n">
+    <row r="2" ht="20" customHeight="1" s="18">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์ ยา</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>ยา + ยาเอกซเรย์</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>MEDICINE</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์ ยา</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H2" s="12" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="n">
+      <c r="G2" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="19" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="18">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์การพยาบาล</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์การพยาบาล</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>NON_MEDICINE</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์มิใช่ยา</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="19" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="18">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>เฝือก</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>เฝือก</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>NON_MEDICINE</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์มิใช่ยา</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="19" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="18">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>เวชศาสตร์ฟื้นฟู</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>เวชศาสตร์ฟื้นฟู</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>NON_MEDICINE</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์มิใช่ยา</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="n">
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="19" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1" s="18">
+      <c r="A6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>ไตเทียม</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>ไตเทียม</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>NON_MEDICINE</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์มิใช่ยา</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="n">
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="19" t="n"/>
+    </row>
+    <row r="7" ht="40" customHeight="1" s="18">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>โสต ศอ นาสิก ลาริงซ์</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>โสต ศอ นาสิก ลาริงซ์</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>NON_MEDICINE</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์มิใช่ยา</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="19" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" s="18">
+      <c r="A8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>จักษุ</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>จักษุ</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>NON_MEDICINE</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์มิใช่ยา</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="19" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="18">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>ตรวจสวนหัวใจ</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>ตรวจสวนหัวใจ</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>NON_MEDICINE</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์มิใช่ยา</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="n">
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="19" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1" s="18">
+      <c r="A10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์ทั่วไป</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์ทั่วไป</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>NON_MEDICINE</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์มิใช่ยา</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="n">
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="19" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1" s="18">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์เภสัช</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์เภสัช</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>NON_MEDICINE</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์มิใช่ยา</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="n">
+      <c r="G11" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="19" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1" s="18">
+      <c r="A12" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>วิสัญญี</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>วิสัญญี</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>NON_MEDICINE</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>เวชภัณฑ์มิใช่ยา</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="n">
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="19" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1" s="18">
+      <c r="A13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>วัสดุการแพทย์ (ซ่อม)</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>วัสดุการแพทย์ (ซ่อม)</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>MEDICAL_SUPPLY</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>วัสดุการแพทย์</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="n">
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="19" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1" s="18">
+      <c r="A14" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>การแพทย์ผ่าตัด</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>การแพทย์ผ่าตัด</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>MEDICAL_SUPPLY</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>วัสดุการแพทย์</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="19" t="n"/>
+    </row>
+    <row r="15" ht="40" customHeight="1" s="18">
+      <c r="A15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>เอกซเรย์ (เวชภัณฑ์+intervention)</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>เอกซเรย์ (เวชภัณฑ์+intervention)</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>MEDICAL_SUPPLY</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>วัสดุการแพทย์</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="19" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" s="18">
+      <c r="A16" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>ทันตกรรม</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>ทันตกรรม</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>MEDICAL_SUPPLY</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>วัสดุการแพทย์</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="n">
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1" s="18">
+      <c r="A17" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>ออกซิเจนเหลว</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>ออกซิเจนเหลว</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>SCIENTIFIC_SUPPLY</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>วัสดุวิทยาศาสตร์</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="n">
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="19" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1" s="18">
+      <c r="A18" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>LAB-COVID</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>LAB-COVID</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>SCIENTIFIC_SUPPLY</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>วัสดุวิทยาศาสตร์</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="n">
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1" s="18">
+      <c r="A19" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>ธนาคารเลือด</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>ธนาคารเลือด</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>SCIENTIFIC_SUPPLY</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>วัสดุวิทยาศาสตร์</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n">
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="19" t="n"/>
+    </row>
+    <row r="20" ht="40" customHeight="1" s="18">
+      <c r="A20" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>พยาธิกายวิภาค</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>พยาธิกายวิภาค</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>SCIENTIFIC_SUPPLY</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>วัสดุวิทยาศาสตร์</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="n">
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="40" customHeight="1" s="18">
+      <c r="A21" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>LAB (ทั่วไป)</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>LAB (ทั่วไป)</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="19" t="inlineStr">
         <is>
           <t>SCIENTIFIC_SUPPLY</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>วัสดุวิทยาศาสตร์</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="n">
+      <c r="G21" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="19" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" s="18">
+      <c r="A22" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>ค่าวัสดุสำนักงาน</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>ค่าวัสดุสำนักงาน</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>GENERAL_SUPPLY</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>วัสดุทั่วไป</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="19" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" s="18">
+      <c r="A23" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>งานบ้าน+น้ำดื่ม</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>งานบ้าน+น้ำดื่ม</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="19" t="inlineStr">
         <is>
           <t>GENERAL_SUPPLY</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>วัสดุทั่วไป</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="n">
+      <c r="G23" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="19" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" s="18">
+      <c r="A24" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>แบบพิมพ์</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>แบบพิมพ์</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="19" t="inlineStr">
         <is>
           <t>GENERAL_SUPPLY</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>วัสดุทั่วไป</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="G24" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="n"/>
+      <c r="I24" s="19" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" s="18">
+      <c r="A25" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>อื่นๆ</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>อื่นๆ</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="19" t="inlineStr">
         <is>
           <t>GENERAL_SUPPLY</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>วัสดุทั่วไป</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="n">
+      <c r="G25" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="19" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" s="18">
+      <c r="A26" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>วัสดุคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>วัสดุคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="19" t="inlineStr">
         <is>
           <t>GENERAL_SUPPLY</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>วัสดุทั่วไป</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="n">
+      <c r="G26" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="19" t="n"/>
+    </row>
+    <row r="27" ht="40" customHeight="1" s="18">
+      <c r="A27" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>วัสดุโฆษณาและเผยแพร่</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>วัสดุโฆษณาและเผยแพร่</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="19" t="inlineStr">
         <is>
           <t>GENERAL_SUPPLY</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>วัสดุทั่วไป</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="n">
+      <c r="G27" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="19" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" s="18">
+      <c r="A28" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>เชื้อเพลิงรถยนต์</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="19" t="inlineStr">
         <is>
           <t>เชื้อเพลิงรถยนต์</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="19" t="inlineStr">
         <is>
           <t>FUEL</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>เชื้อเพลิง</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H28" s="12" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="n">
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="19" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1" s="18">
+      <c r="A29" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>เชื้อเพลิงช่าง</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>เชื้อเพลิงช่าง</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="19" t="inlineStr">
         <is>
           <t>FUEL</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>เชื้อเพลิง</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="n">
+      <c r="G29" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="19" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1" s="18">
+      <c r="A30" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>แก๊ส LPG</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>แก๊ส LPG</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="19" t="inlineStr">
         <is>
           <t>FUEL</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>เชื้อเพลิง</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="n">
+      <c r="G30" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="19" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1" s="18">
+      <c r="A31" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>ออกซิเจนถัง</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>ออกซิเจนถัง</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="19" t="inlineStr">
         <is>
           <t>FUEL</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="19" t="inlineStr">
         <is>
           <t>เชื้อเพลิง</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="n">
+      <c r="G31" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="19" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1" s="18">
+      <c r="A32" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>ค่าวัสดุไฟฟ้า</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="19" t="inlineStr">
         <is>
           <t>ค่าวัสดุไฟฟ้า</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="19" t="inlineStr">
         <is>
           <t>TECHNICIAN</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>วัสดุช่าง</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="n">
+      <c r="G32" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="19" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1" s="18">
+      <c r="A33" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>ค่าวัสุดก่อสร้าง</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>ค่าวัสุดก่อสร้าง</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="19" t="inlineStr">
         <is>
           <t>TECHNICIAN</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>วัสดุช่าง</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="n">
+      <c r="G33" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="19" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1" s="18">
+      <c r="A34" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>ยานพาหนะ</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>ยานพาหนะ</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="19" t="inlineStr">
         <is>
           <t>TECHNICIAN</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>วัสดุช่าง</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="n">
+      <c r="G34" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="19" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1" s="18">
+      <c r="A35" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>โภชนศาสตร์</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="19" t="inlineStr">
         <is>
           <t>โภชนศาสตร์</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="19" t="inlineStr">
         <is>
           <t>NUTRITION</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" s="19" t="inlineStr">
         <is>
           <t>โภชนาการ</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="n">
+      <c r="G35" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="19" t="n"/>
+    </row>
+    <row r="36" ht="40" customHeight="1" s="18">
+      <c r="A36" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>เครื่องแต่งกาย (ซักฟอกและตัดเย็บ)</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>เครื่องแต่งกาย (ซักฟอกและตัดเย็บ)</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="19" t="inlineStr">
         <is>
           <t>UNIFORM</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F36" s="19" t="inlineStr">
         <is>
           <t>เครื่องแต่งกาย</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="G36" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="19" t="n"/>
+    </row>
+    <row r="38" ht="19" customHeight="1" s="18">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>รวม 35 รายการ · ประเภทวัสดุย่อย · โมเดล vpk.budget.material.sub.type</t>
         </is>
@@ -6140,12 +6445,12 @@
   </sheetData>
   <autoFilter ref="A1:I36"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"ถูกต้อง,ต้องแก้ไข,ยังไม่ครบ,ข้าม"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;Lโรงพยาบาลวชิระภูเก็ต · ยืนยันข้อมูลนำเข้า ระบบงบประมาณ</oddHeader>
     <oddFooter>&amp;Lเอกสารยืนยันข้อมูลนำเข้า (Data Migration Sign-off) · ใช้ภายใน&amp;Rหน้า &amp;P / &amp;N</oddFooter>
@@ -6164,182 +6469,181 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" style="18" min="1" max="1"/>
+    <col width="18" customWidth="1" style="18" min="2" max="3"/>
+    <col width="42" customWidth="1" style="18" min="4" max="4"/>
+    <col width="18" customWidth="1" style="18" min="5" max="5"/>
+    <col width="14" customWidth="1" style="18" min="6" max="6"/>
+    <col width="16" customWidth="1" style="18" min="7" max="7"/>
+    <col width="28" customWidth="1" style="18" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="18">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>รหัส</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>ชื่อ</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>กลุ่มแบบฟอร์ม</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>สถานะ</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>ผลยืนยัน</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="12" t="n">
+    <row r="2" ht="20" customHeight="1" s="18">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>supplies_budget</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>วัสดุ</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>material</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G2" s="12" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="n">
+      <c r="F2" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="19" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="18">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>asset_budget</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>asset</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="19" t="n"/>
+    </row>
+    <row r="4" ht="40" customHeight="1" s="18">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>construction_budget</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>ก่อสร้าง</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>construction</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="19" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="18">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>project_budget</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>โครงการ</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="19" t="n"/>
+    </row>
+    <row r="7" ht="19" customHeight="1" s="18">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>รวม 4 รายการ · ประเภทงบประมาณ · โมเดล vpk.budget.type</t>
         </is>
@@ -6348,12 +6652,12 @@
   </sheetData>
   <autoFilter ref="A1:H5"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2 G3 G4 G5" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G2 G3 G4 G5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"ถูกต้อง,ต้องแก้ไข,ยังไม่ครบ,ข้าม"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;Lโรงพยาบาลวชิระภูเก็ต · ยืนยันข้อมูลนำเข้า ระบบงบประมาณ</oddHeader>
     <oddFooter>&amp;Lเอกสารยืนยันข้อมูลนำเข้า (Data Migration Sign-off) · ใช้ภายใน&amp;Rหน้า &amp;P / &amp;N</oddFooter>
@@ -6372,504 +6676,502 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" style="18" min="1" max="1"/>
+    <col width="18" customWidth="1" style="18" min="2" max="3"/>
+    <col width="42" customWidth="1" style="18" min="4" max="5"/>
+    <col width="14" customWidth="1" style="18" min="6" max="6"/>
+    <col width="16" customWidth="1" style="18" min="7" max="7"/>
+    <col width="28" customWidth="1" style="18" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="18">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>รหัส</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>ชื่อ</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>หมวดสินค้า</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>สถานะ</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>ผลยืนยัน</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="12" t="n">
+    <row r="2" ht="20" customHeight="1" s="18">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>medical</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์การแพทย์</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ / 01. ครุภัณฑ์การแพทย์</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G2" s="12" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="n">
+      <c r="F2" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="19" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="18">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>vehicle</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ยานพาหนะและขนส่ง</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="E3" s="19" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>ปิด</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="19" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="18">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>EQ01</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ไฟฟ้าและวิทยุ</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ / 02. ครุภัณฑ์ไฟฟ้าและวิทยุ</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="19" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="18">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>EQ02</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์โรงงาน</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ / 03. ครุภัณฑ์โรงงาน</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="n">
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="19" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1" s="18">
+      <c r="A6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>EQ03</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์การเกษตร</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ / 04. ครุภัณฑ์การเกษตร</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="n">
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="19" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1" s="18">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="19" t="n">
         <v>50</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>EQ04</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์การศึกษา</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ / 05. ครุภัณฑ์การศึกษา</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="19" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" s="18">
+      <c r="A8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="19" t="n">
         <v>60</v>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>computer</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์คอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ / 06. ครุภัณฑ์คอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="19" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="18">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="19" t="n">
         <v>60</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์อื่นๆ</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>ปิด</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="n">
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="19" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1" s="18">
+      <c r="A10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="19" t="n">
         <v>70</v>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>EQ05</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์โฆษณาและเผยแพร่</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ / 07. ครุภัณฑ์โฆษณาและเผยแพร่</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="n">
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="19" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1" s="18">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="19" t="n">
         <v>80</v>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>workshop</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์งานบ้านงานครัว</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ / 08. ครุภัณฑ์งานบ้านงานครัว</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="n">
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="19" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1" s="18">
+      <c r="A12" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="19" t="n">
         <v>90</v>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>EQ06</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ยานพาหนะ</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ / 09. ครุภัณฑ์ยานพาหนะ</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="n">
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="19" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1" s="18">
+      <c r="A13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>EQ07</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์วิทยาศาสตร์</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ / 10. ครุภัณฑ์วิทยาศาสตร์</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="n">
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="19" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1" s="18">
+      <c r="A14" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="19" t="n">
         <v>110</v>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>office</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์สำนักงาน</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ / 11. ครุภัณฑ์สำนักงาน</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="19" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1" s="18">
+      <c r="A15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="19" t="n">
         <v>120</v>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>EQ08</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ก่อสร้าง</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ / 12. ครุภัณฑ์ก่อสร้าง</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="19" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" s="18">
+      <c r="A16" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="19" t="n">
         <v>130</v>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>EQ09</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์สำรวจ</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์ / 13. ครุภัณฑ์สำรวจ</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="19" t="n"/>
+    </row>
+    <row r="18" ht="19" customHeight="1" s="18">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>รวม 15 รายการ · กลุ่มครุภัณฑ์ · โมเดล vpk.budget.asset.category</t>
         </is>
@@ -6878,12 +7180,12 @@
   </sheetData>
   <autoFilter ref="A1:H16"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"ถูกต้อง,ต้องแก้ไข,ยังไม่ครบ,ข้าม"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;Lโรงพยาบาลวชิระภูเก็ต · ยืนยันข้อมูลนำเข้า ระบบงบประมาณ</oddHeader>
     <oddFooter>&amp;Lเอกสารยืนยันข้อมูลนำเข้า (Data Migration Sign-off) · ใช้ภายใน&amp;Rหน้า &amp;P / &amp;N</oddFooter>
@@ -6902,156 +7204,155 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" style="18" min="1" max="1"/>
+    <col width="18" customWidth="1" style="18" min="2" max="3"/>
+    <col width="42" customWidth="1" style="18" min="4" max="4"/>
+    <col width="14" customWidth="1" style="18" min="5" max="5"/>
+    <col width="16" customWidth="1" style="18" min="6" max="6"/>
+    <col width="28" customWidth="1" style="18" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="18">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>รหัส</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>ชื่อ</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>สถานะ</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>ผลยืนยัน</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="12" t="n">
+    <row r="2" ht="20" customHeight="1" s="18">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>material_budget</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>แบบฟอร์มตั้งงบวัสดุ</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="n">
+      <c r="E2" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="19" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="18">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>asset</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>แบบฟอร์มครุภัณฑ์</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="19" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="18">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>construction</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>แบบฟอร์ม ก่อสร้าง</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="19" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="18">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>แบบฟอร์มโครงการ</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>ใช้งาน</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="19" t="n"/>
+    </row>
+    <row r="7" ht="19" customHeight="1" s="18">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>รวม 4 รายการ · แบบฟอร์มคำของบ · โมเดล vpk.budget.request.form.type</t>
         </is>
@@ -7060,12 +7361,12 @@
   </sheetData>
   <autoFilter ref="A1:G5"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2 F3 F4 F5" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="F2 F3 F4 F5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"ถูกต้อง,ต้องแก้ไข,ยังไม่ครบ,ข้าม"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;Lโรงพยาบาลวชิระภูเก็ต · ยืนยันข้อมูลนำเข้า ระบบงบประมาณ</oddHeader>
     <oddFooter>&amp;Lเอกสารยืนยันข้อมูลนำเข้า (Data Migration Sign-off) · ใช้ภายใน&amp;Rหน้า &amp;P / &amp;N</oddFooter>
@@ -7084,182 +7385,178 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" style="18" min="1" max="1"/>
+    <col width="18" customWidth="1" style="18" min="2" max="6"/>
+    <col width="16" customWidth="1" style="18" min="7" max="7"/>
+    <col width="28" customWidth="1" style="18" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="18">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>รหัสแบบฟอร์ม</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>แบบฟอร์ม</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>รหัสประเภทงบ</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>ประเภทงบ</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>ผลยืนยัน</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>หมายเหตุ</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="12" t="n">
+    <row r="2" ht="20" customHeight="1" s="18">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>material_budget</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>แบบฟอร์มตั้งงบวัสดุ</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>supplies_budget</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>วัสดุ</t>
         </is>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="G2" s="12" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="n">
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="19" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="18">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>asset</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>แบบฟอร์มครุภัณฑ์</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>asset_budget</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>ครุภัณฑ์</t>
         </is>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="G3" s="12" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="19" t="n"/>
+    </row>
+    <row r="4" ht="40" customHeight="1" s="18">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>construction</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>แบบฟอร์ม ก่อสร้าง</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>construction_budget</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>ก่อสร้าง</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="12" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="19" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="18">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>แบบฟอร์มโครงการ</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>project_budget</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>โครงการ</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="G5" s="12" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="19" t="n"/>
+    </row>
+    <row r="7" ht="19" customHeight="1" s="18">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>รวม 4 รายการ · ประเภทงบในแบบฟอร์ม · โมเดล vpk.budget.request.form.type.line</t>
         </is>
@@ -7268,12 +7565,12 @@
   </sheetData>
   <autoFilter ref="A1:H5"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2 G3 G4 G5" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G2 G3 G4 G5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"ถูกต้อง,ต้องแก้ไข,ยังไม่ครบ,ข้าม"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;Lโรงพยาบาลวชิระภูเก็ต · ยืนยันข้อมูลนำเข้า ระบบงบประมาณ</oddHeader>
     <oddFooter>&amp;Lเอกสารยืนยันข้อมูลนำเข้า (Data Migration Sign-off) · ใช้ภายใน&amp;Rหน้า &amp;P / &amp;N</oddFooter>
